--- a/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27">
   <si>
     <t>#</t>
   </si>
@@ -83,6 +83,18 @@
   </si>
   <si>
     <t>带有强力攻击技能2</t>
+  </si>
+  <si>
+    <t>米克尔3</t>
+  </si>
+  <si>
+    <t>带有强力攻击技能3</t>
+  </si>
+  <si>
+    <t>米克尔4</t>
+  </si>
+  <si>
+    <t>带有强力攻击技能4</t>
   </si>
 </sst>
 </file>
@@ -117,6 +129,102 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -125,36 +233,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -162,107 +243,38 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -283,13 +295,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -301,7 +415,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -313,157 +451,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -474,6 +486,54 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -503,45 +563,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -565,160 +586,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1080,8 +1092,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <dimension ref="B2:J9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
@@ -1099,6 +1111,9 @@
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="I2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1229,6 +1244,64 @@
         <v>278</v>
       </c>
       <c r="J7" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="2:10">
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>178</v>
+      </c>
+      <c r="J8" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="2:10">
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2</v>
+      </c>
+      <c r="I9" s="1">
+        <v>278</v>
+      </c>
+      <c r="J9" s="1">
         <v>78</v>
       </c>
     </row>
